--- a/Danh sách tồn kho.xlsx
+++ b/Danh sách tồn kho.xlsx
@@ -2089,10 +2089,10 @@
     <t>(SSK048) MH INCELL SS KK Note 10/ N971/ N970</t>
   </si>
   <si>
-    <t>(SST038) MH OLED SS A6 Plus 4G/ A605/ J8 Plus/ J805</t>
-  </si>
-  <si>
-    <t>(SSt041) MH OLED SS A8 Plus/ A730/ A8+ 4G</t>
+    <t>(SS038) MH OLED SS A6 Plus 4G/ A605/ J8 Plus/ J805</t>
+  </si>
+  <si>
+    <t>(SS041) MH OLED SS A8 Plus/ A730/ A8+ 4G</t>
   </si>
 </sst>
 </file>
